--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/144.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/144.xlsx
@@ -426,13 +426,13 @@
         <v>-12.15854538554831</v>
       </c>
       <c r="E2">
-        <v>-14.91148808643677</v>
+        <v>-13.36587915135281</v>
       </c>
       <c r="F2">
-        <v>-3.798241342822684</v>
+        <v>-3.531375018276772</v>
       </c>
       <c r="G2">
-        <v>-9.006860045905263</v>
+        <v>-9.601712110583668</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-12.09879954146758</v>
       </c>
       <c r="E3">
-        <v>-15.27090853995156</v>
+        <v>-13.36261865006728</v>
       </c>
       <c r="F3">
-        <v>-3.698170133437896</v>
+        <v>-3.666869769725151</v>
       </c>
       <c r="G3">
-        <v>-8.964872396830687</v>
+        <v>-9.482625166445004</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-12.13552814072106</v>
       </c>
       <c r="E4">
-        <v>-15.76318989237739</v>
+        <v>-14.32515032887163</v>
       </c>
       <c r="F4">
-        <v>-3.523348004844367</v>
+        <v>-3.19579565332473</v>
       </c>
       <c r="G4">
-        <v>-7.199341908009667</v>
+        <v>-8.409498587708093</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-12.23973777806501</v>
       </c>
       <c r="E5">
-        <v>-15.90136269129943</v>
+        <v>-15.43959419673728</v>
       </c>
       <c r="F5">
-        <v>-3.540769561767159</v>
+        <v>-3.484144948613579</v>
       </c>
       <c r="G5">
-        <v>-8.9841695667791</v>
+        <v>-8.259954624608135</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-12.36056507819795</v>
       </c>
       <c r="E6">
-        <v>-17.48333074419097</v>
+        <v>-16.20870569372601</v>
       </c>
       <c r="F6">
-        <v>-3.810237915132138</v>
+        <v>-3.477767364892104</v>
       </c>
       <c r="G6">
-        <v>-8.044987660561098</v>
+        <v>-7.745327009982889</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.45027947553706</v>
       </c>
       <c r="E7">
-        <v>-16.73102894271872</v>
+        <v>-15.84390994156411</v>
       </c>
       <c r="F7">
-        <v>-3.505318304850046</v>
+        <v>-3.339902597541269</v>
       </c>
       <c r="G7">
-        <v>-8.437247580418264</v>
+        <v>-7.301548380443586</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.45606023254189</v>
       </c>
       <c r="E8">
-        <v>-17.0069624494281</v>
+        <v>-17.69575693141678</v>
       </c>
       <c r="F8">
-        <v>-3.161396768988427</v>
+        <v>-3.825026560970512</v>
       </c>
       <c r="G8">
-        <v>-6.853618326798038</v>
+        <v>-8.213352075051814</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-12.34390191281306</v>
       </c>
       <c r="E9">
-        <v>-17.61461573414734</v>
+        <v>-19.23552866350486</v>
       </c>
       <c r="F9">
-        <v>-3.455382473630325</v>
+        <v>-4.02027532846138</v>
       </c>
       <c r="G9">
-        <v>-6.385493945362935</v>
+        <v>-7.33200870995042</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-12.0854060590572</v>
       </c>
       <c r="E10">
-        <v>-18.84621122459143</v>
+        <v>-20.04451790260513</v>
       </c>
       <c r="F10">
-        <v>-3.793441130192988</v>
+        <v>-3.339213685468053</v>
       </c>
       <c r="G10">
-        <v>-6.155586489297169</v>
+        <v>-6.64179638101331</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.68240333497162</v>
       </c>
       <c r="E11">
-        <v>-18.67553303924233</v>
+        <v>-20.47887101552484</v>
       </c>
       <c r="F11">
-        <v>-3.834102779571895</v>
+        <v>-3.107511967068558</v>
       </c>
       <c r="G11">
-        <v>-6.565590933244827</v>
+        <v>-7.389363911418294</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-11.15566517438349</v>
       </c>
       <c r="E12">
-        <v>-19.96430504250726</v>
+        <v>-21.68381190795978</v>
       </c>
       <c r="F12">
-        <v>-3.280183423028921</v>
+        <v>-3.035195995704804</v>
       </c>
       <c r="G12">
-        <v>-5.631384776972351</v>
+        <v>-5.373192019819052</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-10.5459703829147</v>
       </c>
       <c r="E13">
-        <v>-20.93575781510672</v>
+        <v>-21.66716976598159</v>
       </c>
       <c r="F13">
-        <v>-3.459785176075247</v>
+        <v>-3.208999801394707</v>
       </c>
       <c r="G13">
-        <v>-5.37956150943661</v>
+        <v>-6.166852275767308</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.916456023057323</v>
       </c>
       <c r="E14">
-        <v>-21.84178319524335</v>
+        <v>-21.63436097179601</v>
       </c>
       <c r="F14">
-        <v>-3.253768000212349</v>
+        <v>-3.01490001254549</v>
       </c>
       <c r="G14">
-        <v>-5.327436969920785</v>
+        <v>-6.152984400503302</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-9.324277127579506</v>
       </c>
       <c r="E15">
-        <v>-22.72569150832652</v>
+        <v>-21.57474813995904</v>
       </c>
       <c r="F15">
-        <v>-3.182475102869969</v>
+        <v>-3.061788793583906</v>
       </c>
       <c r="G15">
-        <v>-5.045504290705372</v>
+        <v>-6.167110498319372</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-8.827840335225462</v>
       </c>
       <c r="E16">
-        <v>-22.6389531171836</v>
+        <v>-21.8365029945504</v>
       </c>
       <c r="F16">
-        <v>-3.087299920322762</v>
+        <v>-3.044798004670114</v>
       </c>
       <c r="G16">
-        <v>-4.758099279713544</v>
+        <v>-5.170920997915122</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-8.457558947581203</v>
       </c>
       <c r="E17">
-        <v>-23.24756643839247</v>
+        <v>-24.79395879947976</v>
       </c>
       <c r="F17">
-        <v>-2.744989805230102</v>
+        <v>-2.638735807951439</v>
       </c>
       <c r="G17">
-        <v>-5.39050617298944</v>
+        <v>-4.152931555134771</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-8.231456789501289</v>
       </c>
       <c r="E18">
-        <v>-23.41304593558076</v>
+        <v>-26.19606039326065</v>
       </c>
       <c r="F18">
-        <v>-2.554726543961038</v>
+        <v>-1.717820320358893</v>
       </c>
       <c r="G18">
-        <v>-5.290689914434875</v>
+        <v>-4.788870800501069</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.143520826820843</v>
       </c>
       <c r="E19">
-        <v>-25.15397248308955</v>
+        <v>-25.59922110447172</v>
       </c>
       <c r="F19">
-        <v>-2.014636899324639</v>
+        <v>-1.996355390089764</v>
       </c>
       <c r="G19">
-        <v>-5.350584304331369</v>
+        <v>-3.835165531002287</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-8.16946663706468</v>
       </c>
       <c r="E20">
-        <v>-26.03393649531204</v>
+        <v>-27.54387916911159</v>
       </c>
       <c r="F20">
-        <v>-1.767205813772999</v>
+        <v>-1.18696922418021</v>
       </c>
       <c r="G20">
-        <v>-3.989188662216879</v>
+        <v>-6.392389811721237</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-8.282039749854137</v>
       </c>
       <c r="E21">
-        <v>-27.10372055251405</v>
+        <v>-28.72670299449307</v>
       </c>
       <c r="F21">
-        <v>-2.100525230383709</v>
+        <v>-1.358209009993016</v>
       </c>
       <c r="G21">
-        <v>-5.359095716912835</v>
+        <v>-6.374426791625151</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-8.43855302792166</v>
       </c>
       <c r="E22">
-        <v>-28.03934856723882</v>
+        <v>-29.37476838125676</v>
       </c>
       <c r="F22">
-        <v>-1.374331136212189</v>
+        <v>-1.6322526897477</v>
       </c>
       <c r="G22">
-        <v>-6.213285987501126</v>
+        <v>-4.787384365553937</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-8.607089829715632</v>
       </c>
       <c r="E23">
-        <v>-27.55077150655127</v>
+        <v>-28.65910646298057</v>
       </c>
       <c r="F23">
-        <v>-0.8147943747871512</v>
+        <v>-1.510943984036869</v>
       </c>
       <c r="G23">
-        <v>-4.916856491049294</v>
+        <v>-5.290385344245261</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-8.75287320761838</v>
       </c>
       <c r="E24">
-        <v>-27.09006267490691</v>
+        <v>-30.04702714040644</v>
       </c>
       <c r="F24">
-        <v>-0.6893973322556135</v>
+        <v>-0.6450575258880975</v>
       </c>
       <c r="G24">
-        <v>-3.940907666072148</v>
+        <v>-4.969103520750071</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.855750674808256</v>
       </c>
       <c r="E25">
-        <v>-28.30788254741967</v>
+        <v>-29.23719786937775</v>
       </c>
       <c r="F25">
-        <v>-0.958877563414959</v>
+        <v>-0.6667471702529985</v>
       </c>
       <c r="G25">
-        <v>-4.475041015014779</v>
+        <v>-4.977028966771087</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.900273779637981</v>
       </c>
       <c r="E26">
-        <v>-28.02950366474614</v>
+        <v>-30.241002060288</v>
       </c>
       <c r="F26">
-        <v>-0.5719291133897233</v>
+        <v>-0.5711721019621433</v>
       </c>
       <c r="G26">
-        <v>-5.104160536570179</v>
+        <v>-4.550637322404036</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-8.878487518821681</v>
       </c>
       <c r="E27">
-        <v>-28.19453484300768</v>
+        <v>-28.01374457519945</v>
       </c>
       <c r="F27">
-        <v>-0.6870075200292154</v>
+        <v>-0.5533855008258428</v>
       </c>
       <c r="G27">
-        <v>-4.958231689199105</v>
+        <v>-6.130399858834394</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-8.794361732570216</v>
       </c>
       <c r="E28">
-        <v>-28.87617433606424</v>
+        <v>-28.81760305324903</v>
       </c>
       <c r="F28">
-        <v>-0.3320000427595202</v>
+        <v>-0.5668628381662325</v>
       </c>
       <c r="G28">
-        <v>-5.115651440136989</v>
+        <v>-5.886975445331783</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.651731663477413</v>
       </c>
       <c r="E29">
-        <v>-27.89576877035163</v>
+        <v>-30.94679190522747</v>
       </c>
       <c r="F29">
-        <v>-0.4729467018218002</v>
+        <v>-0.03150689051108174</v>
       </c>
       <c r="G29">
-        <v>-4.745456306299067</v>
+        <v>-4.21062112170211</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.466037917669567</v>
       </c>
       <c r="E30">
-        <v>-27.97310604945462</v>
+        <v>-29.46493709146049</v>
       </c>
       <c r="F30">
-        <v>-0.6854863704974358</v>
+        <v>-0.3355229965684153</v>
       </c>
       <c r="G30">
-        <v>-5.333584652987211</v>
+        <v>-5.224409482193126</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.250144045481374</v>
       </c>
       <c r="E31">
-        <v>-27.81175652056132</v>
+        <v>-30.63780959521011</v>
       </c>
       <c r="F31">
-        <v>-0.4822240510744444</v>
+        <v>-0.2839773282856499</v>
       </c>
       <c r="G31">
-        <v>-4.660461360123819</v>
+        <v>-6.324629565623434</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-8.025191535735537</v>
       </c>
       <c r="E32">
-        <v>-26.77329138959637</v>
+        <v>-29.18423736585804</v>
       </c>
       <c r="F32">
-        <v>-0.6384526803677574</v>
+        <v>-0.9042523789796215</v>
       </c>
       <c r="G32">
-        <v>-4.779925706453959</v>
+        <v>-4.852161810120856</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.808602037606819</v>
       </c>
       <c r="E33">
-        <v>-26.80489108122189</v>
+        <v>-29.41598655167458</v>
       </c>
       <c r="F33">
-        <v>-0.5448255703528926</v>
+        <v>-0.8656867643797979</v>
       </c>
       <c r="G33">
-        <v>-5.066089262868561</v>
+        <v>-5.634063008313621</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.614518117491147</v>
       </c>
       <c r="E34">
-        <v>-27.10052344986464</v>
+        <v>-29.43144676193677</v>
       </c>
       <c r="F34">
-        <v>-0.5937866305816609</v>
+        <v>-0.4803109343285936</v>
       </c>
       <c r="G34">
-        <v>-4.475229716110517</v>
+        <v>-4.321948147096722</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.456310618200793</v>
       </c>
       <c r="E35">
-        <v>-26.74290080053089</v>
+        <v>-28.98468563023604</v>
       </c>
       <c r="F35">
-        <v>-0.9334155315594812</v>
+        <v>-0.7775559057444658</v>
       </c>
       <c r="G35">
-        <v>-4.492864992198215</v>
+        <v>-4.490607200140432</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.335683242040372</v>
       </c>
       <c r="E36">
-        <v>-25.04527552148344</v>
+        <v>-27.42765135523073</v>
       </c>
       <c r="F36">
-        <v>-0.7842193483836772</v>
+        <v>-0.4921198374870678</v>
       </c>
       <c r="G36">
-        <v>-4.376982656141566</v>
+        <v>-5.139937602213083</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.257018987726353</v>
       </c>
       <c r="E37">
-        <v>-24.15621833345355</v>
+        <v>-27.03000605261719</v>
       </c>
       <c r="F37">
-        <v>-1.091061577647112</v>
+        <v>-0.4436893187399718</v>
       </c>
       <c r="G37">
-        <v>-4.788304697213854</v>
+        <v>-5.179167566853446</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.213672486386613</v>
       </c>
       <c r="E38">
-        <v>-24.94248368998333</v>
+        <v>-26.65974896080205</v>
       </c>
       <c r="F38">
-        <v>-0.9055929860370411</v>
+        <v>-1.524024603045441</v>
       </c>
       <c r="G38">
-        <v>-4.685171272028938</v>
+        <v>-6.916707393139928</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.201234954692387</v>
       </c>
       <c r="E39">
-        <v>-24.07769912263456</v>
+        <v>-24.83079793553216</v>
       </c>
       <c r="F39">
-        <v>-1.279609685409756</v>
+        <v>-0.4568760460448784</v>
       </c>
       <c r="G39">
-        <v>-4.924576683246874</v>
+        <v>-4.484486001438319</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.210965201012344</v>
       </c>
       <c r="E40">
-        <v>-23.57225802474244</v>
+        <v>-26.42113913686389</v>
       </c>
       <c r="F40">
-        <v>-0.8798815204998817</v>
+        <v>-0.702572973619112</v>
       </c>
       <c r="G40">
-        <v>-5.212541176434839</v>
+        <v>-4.899264252053607</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-7.234205570221969</v>
       </c>
       <c r="E41">
-        <v>-23.55557512649818</v>
+        <v>-24.8162434200715</v>
       </c>
       <c r="F41">
-        <v>-0.9710127099920137</v>
+        <v>-1.979614826710611</v>
       </c>
       <c r="G41">
-        <v>-4.933247002014225</v>
+        <v>-5.329439849972044</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-7.266484087008696</v>
       </c>
       <c r="E42">
-        <v>-23.73991571792842</v>
+        <v>-24.85773329892978</v>
       </c>
       <c r="F42">
-        <v>-1.008791222751864</v>
+        <v>-0.8869480162945724</v>
       </c>
       <c r="G42">
-        <v>-4.219642358296625</v>
+        <v>-3.925655982772725</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-7.300207687850833</v>
       </c>
       <c r="E43">
-        <v>-22.2215500824746</v>
+        <v>-22.39405324284878</v>
       </c>
       <c r="F43">
-        <v>-0.7929819932138037</v>
+        <v>-1.065506107142624</v>
       </c>
       <c r="G43">
-        <v>-4.378071825623986</v>
+        <v>-5.438197892028181</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-7.338755262450381</v>
       </c>
       <c r="E44">
-        <v>-22.41899607768303</v>
+        <v>-24.72208286003002</v>
       </c>
       <c r="F44">
-        <v>-0.8785931757376716</v>
+        <v>-0.9946732763686791</v>
       </c>
       <c r="G44">
-        <v>-5.829997646055387</v>
+        <v>-5.526715258657214</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-7.381715619775438</v>
       </c>
       <c r="E45">
-        <v>-22.10483772187491</v>
+        <v>-21.99573319760811</v>
       </c>
       <c r="F45">
-        <v>-0.9013510297425364</v>
+        <v>-0.4175257051639544</v>
       </c>
       <c r="G45">
-        <v>-4.15175300092279</v>
+        <v>-4.641568076731198</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-7.438652720257859</v>
       </c>
       <c r="E46">
-        <v>-22.39708732043393</v>
+        <v>-21.76061935560387</v>
       </c>
       <c r="F46">
-        <v>-0.8567206133395374</v>
+        <v>-1.017796174587053</v>
       </c>
       <c r="G46">
-        <v>-4.083545831177186</v>
+        <v>-4.831785402326642</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.514981351533895</v>
       </c>
       <c r="E47">
-        <v>-21.38493715192754</v>
+        <v>-21.9800827914376</v>
       </c>
       <c r="F47">
-        <v>-0.7472786160530944</v>
+        <v>-1.02062388149907</v>
       </c>
       <c r="G47">
-        <v>-4.470114923252344</v>
+        <v>-4.265645699110337</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.621671723673495</v>
       </c>
       <c r="E48">
-        <v>-20.59123151260316</v>
+        <v>-22.89408281430174</v>
       </c>
       <c r="F48">
-        <v>-0.7617354755021833</v>
+        <v>-0.8403094607907962</v>
       </c>
       <c r="G48">
-        <v>-4.26844642063656</v>
+        <v>-5.427157222654712</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.768811044483234</v>
       </c>
       <c r="E49">
-        <v>-19.10419838880841</v>
+        <v>-20.79718198199799</v>
       </c>
       <c r="F49">
-        <v>-0.6410238269214733</v>
+        <v>-1.188214017029745</v>
       </c>
       <c r="G49">
-        <v>-5.231447702009617</v>
+        <v>-3.949114508464001</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.959863292713703</v>
       </c>
       <c r="E50">
-        <v>-20.20937247038036</v>
+        <v>-20.94058516839889</v>
       </c>
       <c r="F50">
-        <v>-0.6496376033955484</v>
+        <v>-1.661334281472914</v>
       </c>
       <c r="G50">
-        <v>-4.487809789159748</v>
+        <v>-4.799828706236057</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.202026372425674</v>
       </c>
       <c r="E51">
-        <v>-19.31896579709618</v>
+        <v>-20.76065983912613</v>
       </c>
       <c r="F51">
-        <v>-0.6674772586800161</v>
+        <v>-0.8960836238677848</v>
       </c>
       <c r="G51">
-        <v>-4.460024380448645</v>
+        <v>-4.505865504530933</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.490201471068001</v>
       </c>
       <c r="E52">
-        <v>-18.78668896223461</v>
+        <v>-20.12422810208814</v>
       </c>
       <c r="F52">
-        <v>-1.029576571039049</v>
+        <v>-0.5962873022221398</v>
       </c>
       <c r="G52">
-        <v>-4.885340097515432</v>
+        <v>-5.79750464158744</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.826433419213863</v>
       </c>
       <c r="E53">
-        <v>-18.10893037140262</v>
+        <v>-19.70079766847493</v>
       </c>
       <c r="F53">
-        <v>-1.046010687323564</v>
+        <v>-0.885508427617438</v>
       </c>
       <c r="G53">
-        <v>-4.58468959382098</v>
+        <v>-3.798931610074963</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-9.201562141652222</v>
       </c>
       <c r="E54">
-        <v>-18.43643414011134</v>
+        <v>-17.79304213852356</v>
       </c>
       <c r="F54">
-        <v>-1.028271597364727</v>
+        <v>-0.6264988681180204</v>
       </c>
       <c r="G54">
-        <v>-4.368934719935598</v>
+        <v>-3.890166934591738</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-9.611665017725754</v>
       </c>
       <c r="E55">
-        <v>-17.99051983305005</v>
+        <v>-17.93686647300717</v>
       </c>
       <c r="F55">
-        <v>-0.3880505625187531</v>
+        <v>-0.8111273037399511</v>
       </c>
       <c r="G55">
-        <v>-4.185742371974488</v>
+        <v>-5.434238479563213</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-10.05057204872001</v>
       </c>
       <c r="E56">
-        <v>-17.06425670257314</v>
+        <v>-20.42380930006557</v>
       </c>
       <c r="F56">
-        <v>-0.7610441878700941</v>
+        <v>-0.5487127765223387</v>
       </c>
       <c r="G56">
-        <v>-5.301452497983045</v>
+        <v>-5.24378941578002</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-10.50575536675506</v>
       </c>
       <c r="E57">
-        <v>-17.56710298485887</v>
+        <v>-17.82876274149607</v>
       </c>
       <c r="F57">
-        <v>-0.5806489981601329</v>
+        <v>-1.018424113982525</v>
       </c>
       <c r="G57">
-        <v>-5.020522914066031</v>
+        <v>-5.698456429597985</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-10.97633442105167</v>
       </c>
       <c r="E58">
-        <v>-17.43794184921209</v>
+        <v>-17.00738812598482</v>
       </c>
       <c r="F58">
-        <v>-0.795916600275113</v>
+        <v>-1.202786487010661</v>
       </c>
       <c r="G58">
-        <v>-5.072147561205426</v>
+        <v>-7.070101520702059</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-11.44883495341747</v>
       </c>
       <c r="E59">
-        <v>-18.74631308798222</v>
+        <v>-16.37742304982978</v>
       </c>
       <c r="F59">
-        <v>-0.1339639528574791</v>
+        <v>-0.8615057807630377</v>
       </c>
       <c r="G59">
-        <v>-5.406284233029607</v>
+        <v>-5.26745319529473</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-11.92257208326708</v>
       </c>
       <c r="E60">
-        <v>-17.89988695426054</v>
+        <v>-17.52062725611815</v>
       </c>
       <c r="F60">
-        <v>-0.8218774994939542</v>
+        <v>-0.7061854068122293</v>
       </c>
       <c r="G60">
-        <v>-6.094493681915458</v>
+        <v>-5.802248653345216</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-12.38772579501908</v>
       </c>
       <c r="E61">
-        <v>-17.53835170338417</v>
+        <v>-16.1913480528546</v>
       </c>
       <c r="F61">
-        <v>-0.4143503748034983</v>
+        <v>-0.6964456154322768</v>
       </c>
       <c r="G61">
-        <v>-6.257322864264512</v>
+        <v>-7.227600724732886</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-12.84159677561743</v>
       </c>
       <c r="E62">
-        <v>-16.66713217447049</v>
+        <v>-16.78644840762459</v>
       </c>
       <c r="F62">
-        <v>-0.4901386213868531</v>
+        <v>-0.06075714691629061</v>
       </c>
       <c r="G62">
-        <v>-5.610491924074011</v>
+        <v>-4.805589055474389</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-13.28251349851348</v>
       </c>
       <c r="E63">
-        <v>-16.97756812464431</v>
+        <v>-16.93911685184518</v>
       </c>
       <c r="F63">
-        <v>-0.5808485451054783</v>
+        <v>-0.8642867683505494</v>
       </c>
       <c r="G63">
-        <v>-5.714942946383556</v>
+        <v>-5.427974927402912</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-13.70200403797059</v>
       </c>
       <c r="E64">
-        <v>-15.46761186542274</v>
+        <v>-16.61832428161582</v>
       </c>
       <c r="F64">
-        <v>-1.192550203826219</v>
+        <v>-0.8403023341141767</v>
       </c>
       <c r="G64">
-        <v>-6.726155702445018</v>
+        <v>-6.118587832350274</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-14.1030562532645</v>
       </c>
       <c r="E65">
-        <v>-16.32071749830573</v>
+        <v>-16.95006670199573</v>
       </c>
       <c r="F65">
-        <v>-0.1936791681050389</v>
+        <v>-0.9599917005264706</v>
       </c>
       <c r="G65">
-        <v>-7.293205805684623</v>
+        <v>-8.208992086576593</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-14.47318586698064</v>
       </c>
       <c r="E66">
-        <v>-15.55356683056233</v>
+        <v>-15.75045129499381</v>
       </c>
       <c r="F66">
-        <v>-0.5031242180404988</v>
+        <v>-1.171657163536784</v>
       </c>
       <c r="G66">
-        <v>-6.464602741569359</v>
+        <v>-7.149978363473594</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-14.81233486960889</v>
       </c>
       <c r="E67">
-        <v>-17.35348580896904</v>
+        <v>-16.20477497828735</v>
       </c>
       <c r="F67">
-        <v>-0.5949332336644391</v>
+        <v>-1.223279641556448</v>
       </c>
       <c r="G67">
-        <v>-7.350858956251031</v>
+        <v>-8.18988361772392</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-15.11358131519647</v>
       </c>
       <c r="E68">
-        <v>-16.81069838593566</v>
+        <v>-16.49935674096031</v>
       </c>
       <c r="F68">
-        <v>-0.5817678863893909</v>
+        <v>-0.8966616765269203</v>
       </c>
       <c r="G68">
-        <v>-7.26691676355727</v>
+        <v>-6.646507287315693</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-15.37115050047588</v>
       </c>
       <c r="E69">
-        <v>-15.0893891878281</v>
+        <v>-15.61937008636778</v>
       </c>
       <c r="F69">
-        <v>-0.6856201936472904</v>
+        <v>-1.413587246591145</v>
       </c>
       <c r="G69">
-        <v>-7.830073665242692</v>
+        <v>-7.54205289278056</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-15.58577130781923</v>
       </c>
       <c r="E70">
-        <v>-15.2056939857671</v>
+        <v>-14.82897929001702</v>
       </c>
       <c r="F70">
-        <v>-0.7728768466172999</v>
+        <v>-0.4419448666741153</v>
       </c>
       <c r="G70">
-        <v>-8.081483114586025</v>
+        <v>-6.748743554659466</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-15.74900188941208</v>
       </c>
       <c r="E71">
-        <v>-15.13012281152709</v>
+        <v>-16.89932515073978</v>
       </c>
       <c r="F71">
-        <v>-1.097975245820963</v>
+        <v>-0.681250749026593</v>
       </c>
       <c r="G71">
-        <v>-7.17788626236965</v>
+        <v>-8.49508612153487</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-15.86687734869864</v>
       </c>
       <c r="E72">
-        <v>-16.05374584165753</v>
+        <v>-15.68122451283855</v>
       </c>
       <c r="F72">
-        <v>-0.8809663590519576</v>
+        <v>-1.752881985620807</v>
       </c>
       <c r="G72">
-        <v>-8.508444172785829</v>
+        <v>-8.203235047883801</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-15.93512994061913</v>
       </c>
       <c r="E73">
-        <v>-16.04147367709675</v>
+        <v>-15.22388486585591</v>
       </c>
       <c r="F73">
-        <v>-0.7341409836315664</v>
+        <v>-1.258107710195834</v>
       </c>
       <c r="G73">
-        <v>-7.866559187631</v>
+        <v>-8.483562112512667</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-15.95794558800173</v>
       </c>
       <c r="E74">
-        <v>-15.44408644295289</v>
+        <v>-15.96828900865879</v>
       </c>
       <c r="F74">
-        <v>-1.303196609461353</v>
+        <v>-1.250548681861442</v>
       </c>
       <c r="G74">
-        <v>-7.529817116467413</v>
+        <v>-9.287703555638256</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-15.94172630693601</v>
       </c>
       <c r="E75">
-        <v>-16.28114769242671</v>
+        <v>-16.93176261005672</v>
       </c>
       <c r="F75">
-        <v>-1.305039251293967</v>
+        <v>-1.265369001818124</v>
       </c>
       <c r="G75">
-        <v>-7.460120201229137</v>
+        <v>-7.291106919812725</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-15.88706168382158</v>
       </c>
       <c r="E76">
-        <v>-16.22966799990751</v>
+        <v>-16.99910101855078</v>
       </c>
       <c r="F76">
-        <v>-1.193773616645895</v>
+        <v>-2.001216575397205</v>
       </c>
       <c r="G76">
-        <v>-7.460722720517285</v>
+        <v>-6.23234479817071</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-15.80594486938232</v>
       </c>
       <c r="E77">
-        <v>-15.81658060092782</v>
+        <v>-17.66767586409522</v>
       </c>
       <c r="F77">
-        <v>-1.810288157643656</v>
+        <v>-1.343630205188438</v>
       </c>
       <c r="G77">
-        <v>-7.541930402595606</v>
+        <v>-7.516584865946946</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-15.69823968482533</v>
       </c>
       <c r="E78">
-        <v>-17.83540601286532</v>
+        <v>-18.71901091818998</v>
       </c>
       <c r="F78">
-        <v>-1.112898506662149</v>
+        <v>-1.922241912511986</v>
       </c>
       <c r="G78">
-        <v>-7.532283472894171</v>
+        <v>-8.934561041873121</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-15.57591981922722</v>
       </c>
       <c r="E79">
-        <v>-17.85547168119331</v>
+        <v>-16.68383318661078</v>
       </c>
       <c r="F79">
-        <v>-2.010500259473511</v>
+        <v>-1.93345375854034</v>
       </c>
       <c r="G79">
-        <v>-7.419172063453892</v>
+        <v>-6.967911600995836</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-15.44233102875181</v>
       </c>
       <c r="E80">
-        <v>-17.51272054050076</v>
+        <v>-17.91891560204077</v>
       </c>
       <c r="F80">
-        <v>-1.435721912318284</v>
+        <v>-1.460725461311242</v>
       </c>
       <c r="G80">
-        <v>-6.461381580759648</v>
+        <v>-6.9427282810786</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-15.30354282050561</v>
       </c>
       <c r="E81">
-        <v>-18.19910587431736</v>
+        <v>-19.57227504766324</v>
       </c>
       <c r="F81">
-        <v>-0.9931830091022505</v>
+        <v>-2.685691896491261</v>
       </c>
       <c r="G81">
-        <v>-6.528542618114843</v>
+        <v>-7.9673984047572</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-15.16997819631213</v>
       </c>
       <c r="E82">
-        <v>-20.14334731934852</v>
+        <v>-19.23140775215788</v>
       </c>
       <c r="F82">
-        <v>-1.234029045457493</v>
+        <v>-1.944746373570381</v>
       </c>
       <c r="G82">
-        <v>-7.215355016783121</v>
+        <v>-8.461566847949749</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-15.04077004168162</v>
       </c>
       <c r="E83">
-        <v>-19.82693831195859</v>
+        <v>-19.02333342845344</v>
       </c>
       <c r="F83">
-        <v>-1.525050844478646</v>
+        <v>-2.274031299361508</v>
       </c>
       <c r="G83">
-        <v>-7.401248769904277</v>
+        <v>-5.831831688284143</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-14.92827203894414</v>
       </c>
       <c r="E84">
-        <v>-20.26153596247471</v>
+        <v>-19.11016691755052</v>
       </c>
       <c r="F84">
-        <v>-2.006098348881547</v>
+        <v>-2.483348918352183</v>
       </c>
       <c r="G84">
-        <v>-6.851797526751438</v>
+        <v>-7.355202391998555</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-14.83134297418609</v>
       </c>
       <c r="E85">
-        <v>-21.03923344618198</v>
+        <v>-19.0891366842589</v>
       </c>
       <c r="F85">
-        <v>-1.888457506070874</v>
+        <v>-2.594485480968145</v>
       </c>
       <c r="G85">
-        <v>-6.0140838413121</v>
+        <v>-6.008806831722502</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-14.76065790952211</v>
       </c>
       <c r="E86">
-        <v>-21.85036465348788</v>
+        <v>-22.23286673901977</v>
       </c>
       <c r="F86">
-        <v>-1.454190298851181</v>
+        <v>-3.434584455695817</v>
       </c>
       <c r="G86">
-        <v>-6.27636181166086</v>
+        <v>-6.894619433301911</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-14.71760737603882</v>
       </c>
       <c r="E87">
-        <v>-23.08610369764898</v>
+        <v>-24.38880528696151</v>
       </c>
       <c r="F87">
-        <v>-2.272990012722107</v>
+        <v>-2.154605619984135</v>
       </c>
       <c r="G87">
-        <v>-6.16330006040367</v>
+        <v>-6.442061236992462</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-14.70784905053999</v>
       </c>
       <c r="E88">
-        <v>-24.14714780001619</v>
+        <v>-23.43607775438377</v>
       </c>
       <c r="F88">
-        <v>-2.642715660916938</v>
+        <v>-3.005664631499605</v>
       </c>
       <c r="G88">
-        <v>-4.995326351966638</v>
+        <v>-7.364743384242734</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-14.74105694611898</v>
       </c>
       <c r="E89">
-        <v>-26.40732729114049</v>
+        <v>-25.38830289909047</v>
       </c>
       <c r="F89">
-        <v>-2.523046090828588</v>
+        <v>-2.48679822983601</v>
       </c>
       <c r="G89">
-        <v>-5.787520036240998</v>
+        <v>-5.772324632215743</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-14.81674408804059</v>
       </c>
       <c r="E90">
-        <v>-27.16615009518379</v>
+        <v>-24.71368706921979</v>
       </c>
       <c r="F90">
-        <v>-2.814584177978174</v>
+        <v>-2.776457249916927</v>
       </c>
       <c r="G90">
-        <v>-5.563604667601313</v>
+        <v>-5.182653571306298</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-14.94700425801521</v>
       </c>
       <c r="E91">
-        <v>-28.0555695611343</v>
+        <v>-29.64097925427167</v>
       </c>
       <c r="F91">
-        <v>-2.321148925904705</v>
+        <v>-3.262854512902182</v>
       </c>
       <c r="G91">
-        <v>-4.769020769447599</v>
+        <v>-6.115522267180909</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-15.12674795706174</v>
       </c>
       <c r="E92">
-        <v>-30.01402815031254</v>
+        <v>-28.82577242035887</v>
       </c>
       <c r="F92">
-        <v>-2.418097859077204</v>
+        <v>-4.094207471711839</v>
       </c>
       <c r="G92">
-        <v>-5.97052368310637</v>
+        <v>-4.506170074720546</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-15.35793119043869</v>
       </c>
       <c r="E93">
-        <v>-31.49510859502421</v>
+        <v>-30.79349626735682</v>
       </c>
       <c r="F93">
-        <v>-2.961107065568716</v>
+        <v>-4.084827181574691</v>
       </c>
       <c r="G93">
-        <v>-5.776366808319193</v>
+        <v>-5.690338971935692</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-15.62625156726714</v>
       </c>
       <c r="E94">
-        <v>-34.13998648157412</v>
+        <v>-34.90930175989319</v>
       </c>
       <c r="F94">
-        <v>-3.687721633660785</v>
+        <v>-4.010130108367075</v>
       </c>
       <c r="G94">
-        <v>-6.089153771960613</v>
+        <v>-5.790370415950311</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-15.91797084737458</v>
       </c>
       <c r="E95">
-        <v>-34.92007952803144</v>
+        <v>-33.51311661740333</v>
       </c>
       <c r="F95">
-        <v>-3.656134619177345</v>
+        <v>-4.682322206380982</v>
       </c>
       <c r="G95">
-        <v>-6.286227237367888</v>
+        <v>-5.825409229937957</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-16.2127552033685</v>
       </c>
       <c r="E96">
-        <v>-37.84073016046347</v>
+        <v>-35.20828972777562</v>
       </c>
       <c r="F96">
-        <v>-3.647341092081867</v>
+        <v>-4.460812427400297</v>
       </c>
       <c r="G96">
-        <v>-6.130456138108561</v>
+        <v>-6.086541751530128</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-16.48174173286543</v>
       </c>
       <c r="E97">
-        <v>-39.43189327982758</v>
+        <v>-38.56101112222748</v>
       </c>
       <c r="F97">
-        <v>-3.615233038352248</v>
+        <v>-4.825670555464026</v>
       </c>
       <c r="G97">
-        <v>-6.346780425826697</v>
+        <v>-7.28163544902487</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-16.69865713926919</v>
       </c>
       <c r="E98">
-        <v>-42.72040996979869</v>
+        <v>-40.20202368346803</v>
       </c>
       <c r="F98">
-        <v>-4.09132829435757</v>
+        <v>-4.771801590603311</v>
       </c>
       <c r="G98">
-        <v>-5.882072527388122</v>
+        <v>-5.907421374582322</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-16.84338643244505</v>
       </c>
       <c r="E99">
-        <v>-42.77241496530278</v>
+        <v>-42.89993905759578</v>
       </c>
       <c r="F99">
-        <v>-4.851398649913297</v>
+        <v>-4.213475572350626</v>
       </c>
       <c r="G99">
-        <v>-6.376052269484934</v>
+        <v>-8.392148018536773</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-16.88479723423491</v>
       </c>
       <c r="E100">
-        <v>-46.35830975064659</v>
+        <v>-45.14025666172245</v>
       </c>
       <c r="F100">
-        <v>-4.618990598675516</v>
+        <v>-5.173359727698475</v>
       </c>
       <c r="G100">
-        <v>-6.798520917387947</v>
+        <v>-7.389370532509372</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-16.83720320128226</v>
       </c>
       <c r="E101">
-        <v>-47.90349753764784</v>
+        <v>-45.3994121722334</v>
       </c>
       <c r="F101">
-        <v>-5.147181860769219</v>
+        <v>-5.393127430172177</v>
       </c>
       <c r="G101">
-        <v>-7.436999351182867</v>
+        <v>-7.575327185995774</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-16.65406368944852</v>
       </c>
       <c r="E102">
-        <v>-50.26581562789665</v>
+        <v>-50.37836292452779</v>
       </c>
       <c r="F102">
-        <v>-4.66289013479854</v>
+        <v>-5.790445194678752</v>
       </c>
       <c r="G102">
-        <v>-8.430550346792318</v>
+        <v>-8.936156724823048</v>
       </c>
     </row>
   </sheetData>
